--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationrange.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationrange.xlsx
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) (http://jpfhir.jp, office@hlfhir.jp)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationrange.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationrange.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="119">
   <si>
     <t>Property</t>
   </si>
@@ -338,6 +338,9 @@
     <t>Range.low</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
     <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationSimpleQuantity}
 </t>
   </si>
@@ -345,23 +348,38 @@
     <t>薬剤の上限量</t>
   </si>
   <si>
-    <t>薬剤に関する数量と単位を定めた簡易データイプ</t>
-  </si>
-  <si>
-    <t>薬剤に関する簡易的な数量と単位を定めている。ValueおよびCodeを必須とし、comparatorは記述不可。単位についてはMERIT9医薬品単位略号の利用を推進している。(**SHOULD**)</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
-  </si>
-  <si>
-    <t>SN (see also Range) or CQ</t>
-  </si>
-  <si>
-    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
+    <t>The low limit. The boundary is inclusive.</t>
+  </si>
+  <si>
+    <t>If the low element is missing, the low boundary is not known.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
+    <t>NR.1</t>
+  </si>
+  <si>
+    <t>./low</t>
   </si>
   <si>
     <t>Range.high</t>
+  </si>
+  <si>
+    <t>High limit</t>
+  </si>
+  <si>
+    <t>The high limit. The boundary is inclusive.</t>
+  </si>
+  <si>
+    <t>If the high element is missing, the high boundary is not known.</t>
+  </si>
+  <si>
+    <t>NR.2</t>
+  </si>
+  <si>
+    <t>./high</t>
   </si>
 </sst>
 </file>
@@ -1170,19 +1188,19 @@
         <v>76</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1241,24 +1259,24 @@
         <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1278,19 +1296,19 @@
         <v>76</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -1340,7 +1358,7 @@
         <v>76</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>77</v>
@@ -1349,16 +1367,16 @@
         <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationrange.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationrange.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev</t>
+    <t>2.0.0-dev-temp</t>
   </si>
   <si>
     <t>Name</t>
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -686,43 +686,43 @@
   <dimension ref="A1:AL6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="16.44921875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="16.44921875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="12.64453125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="14.1015625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="14.1015625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="78.26953125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="67.1015625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="15.6640625" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="19.625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="18.1875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="15.59375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="44.546875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="94.8359375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="38.19140625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="81.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationrange.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationrange.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev-temp</t>
+    <t>2.0.0-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationrange.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationrange.xlsx
@@ -266,8 +266,8 @@
 </t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-rng-2:If present, low SHALL have a lower value than high {low.empty() or high.empty() or (low &lt;= high)}</t>
+    <t>ele-1:空のParametersリソースでない限り、すべてのFHIR要素には@valueまたはchildrenが必要です / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+rng-2:存在する場合、低い値は高よりも低い値を持つものとします / If present, low SHALL have a lower value than high {low.empty() or high.empty() or (low &lt;= high)}</t>
   </si>
   <si>
     <t>NR and also possibly SN (but see also quantity)</t>
@@ -286,10 +286,10 @@
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
   </si>
   <si>
     <t>Element.id</t>
@@ -309,13 +309,13 @@
 </t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
@@ -331,8 +331,8 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Range.low</t>
@@ -348,13 +348,13 @@
     <t>薬剤の上限量</t>
   </si>
   <si>
-    <t>The low limit. The boundary is inclusive.</t>
-  </si>
-  <si>
-    <t>If the low element is missing, the low boundary is not known.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>低制限。境界は包括的です。 / The low limit. The boundary is inclusive.</t>
+  </si>
+  <si>
+    <t>低要素が欠落している場合、低境界は不明です。 / If the low element is missing, the low boundary is not known.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -367,13 +367,13 @@
     <t>Range.high</t>
   </si>
   <si>
-    <t>High limit</t>
-  </si>
-  <si>
-    <t>The high limit. The boundary is inclusive.</t>
-  </si>
-  <si>
-    <t>If the high element is missing, the high boundary is not known.</t>
+    <t>高制限 / High limit</t>
+  </si>
+  <si>
+    <t>高制限。境界は包括的です。 / The high limit. The boundary is inclusive.</t>
+  </si>
+  <si>
+    <t>高い要素が欠落している場合、高境界は不明です。 / If the high element is missing, the high boundary is not known.</t>
   </si>
   <si>
     <t>NR.2</t>
